--- a/output/pdf_financials_xlsx/BCT.xlsx
+++ b/output/pdf_financials_xlsx/BCT.xlsx
@@ -4565,40 +4565,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.502636</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.042207</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.726211</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.812594</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.747531</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.046338</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.446886</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.22816</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.42195</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>11.033557</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>28.035166</v>
       </c>
     </row>
     <row r="93">
@@ -7826,7 +7826,11 @@
           <t>Share-based payment reserved</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -7900,7 +7904,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -8516,7 +8524,11 @@
           <t>Share-based payment reserved</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -8590,7 +8602,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -9288,7 +9304,11 @@
           <t>Share-based payment reserved</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -9362,7 +9382,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -10906,7 +10930,11 @@
           <t>Share-based payment reserve (Note 8) 2,178,130</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -10980,7 +11008,11 @@
           <t>Warrant reserve (Note 7) 16,193,475</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -12316,7 +12348,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -12390,7 +12426,11 @@
           <t>Warrant reserve (Note 7(c))</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -13286,7 +13326,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -13356,7 +13400,11 @@
           <t>Warrant reserve (Note 8(c)(d))</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -14116,7 +14164,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>1e-06</v>
       </c>
@@ -14190,7 +14242,11 @@
           <t>Warrant reserve (Note 8(c))</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BCT.xlsx
+++ b/output/pdf_financials_xlsx/BCT.xlsx
@@ -826,19 +826,19 @@
         <v>2.177196</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.002485</v>
+        <v>3.218236</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.43616</v>
+        <v>4.976503</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.352204</v>
+        <v>5.064993</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.08509700000000001</v>
+        <v>3.939439</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>6.545164</v>
+        <v>6.973498</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>8.021489000000001</v>
@@ -914,25 +914,25 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.009227000000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004738</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.006428</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.015991</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.009771</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003149</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1669,25 +1669,25 @@
         <v>-0.001242</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.488811</v>
+        <v>-3.498038</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.214782</v>
+        <v>-2.21952</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.220721</v>
+        <v>-3.227149</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.412663</v>
+        <v>-5.428654</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.712789</v>
+        <v>-4.72256</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-4.024536</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.428334</v>
+        <v>-0.431483</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-26.838903</v>
@@ -1763,25 +1763,25 @@
         <v>-0.001242</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.488246</v>
+        <v>-3.497473</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.213597</v>
+        <v>-2.218335</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.220431</v>
+        <v>-3.226859</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.395769</v>
+        <v>-5.41176</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.697532</v>
+        <v>-4.707303</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-4.009281</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.413078</v>
+        <v>-0.416227</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-26.838903</v>
@@ -2004,7 +2004,7 @@
         <v>0.171865</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.264429</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.9384479999999999</v>
@@ -2013,10 +2013,10 @@
         <v>0.192916</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.157034</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.021249</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>41.041652</v>
@@ -2090,7 +2090,7 @@
         <v>1.071865</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.75</v>
+        <v>2.014429</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>2.279491</v>
@@ -2099,10 +2099,10 @@
         <v>0.192916</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.157034</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.021249</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>41.041652</v>
@@ -2606,7 +2606,7 @@
         <v>0.013164</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.279843</v>
+        <v>0.015414</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.147734</v>
@@ -2615,10 +2615,10 @@
         <v>0.010667</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.165717</v>
+        <v>0.008683</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.238948</v>
+        <v>0.217699</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>1.280945</v>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -36480,7 +36480,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -36624,7 +36624,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -36694,7 +36694,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -37638,7 +37638,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -38524,7 +38524,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">

--- a/output/pdf_financials_xlsx/BCT.xlsx
+++ b/output/pdf_financials_xlsx/BCT.xlsx
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002264</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002264</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -6483,7 +6483,7 @@
         <v>-0.000992</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.216702</v>
+        <v>-1.218966</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.566283</v>
@@ -26420,7 +26420,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -26496,7 +26500,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -29856,7 +29864,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
